--- a/data/file_generation/input/data_57/2025-10-19_03_00_荷甲_阿贾克斯[3]VS阿尔克马尔[4]_标盘.xlsx
+++ b/data/file_generation/input/data_57/2025-10-19_03_00_荷甲_阿贾克斯[3]VS阿尔克马尔[4]_标盘.xlsx
@@ -5932,26 +5932,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{799451AF-1703-46FB-A45B-D818BE7A2C4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2188BB2-887E-414E-889A-DB45B24F7A69}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85FEAA2A-A3DA-4E03-8203-520B2159FB25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D89EBD05-1438-47AE-8A52-947210E75E58}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0501FEC-2777-46BB-B3AE-0CF7E0E9CBCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F53924A-07F1-4B4E-8DE2-7722C8E8E16A}"/>
 </file>